--- a/datasets/day1_excel_foundations/05_functions_and_data_tips/d1_m5_functions_answers.xlsx
+++ b/datasets/day1_excel_foundations/05_functions_and_data_tips/d1_m5_functions_answers.xlsx
@@ -611,7 +611,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>119.7</v>
+        <v>120</v>
       </c>
       <c r="I3">
         <f>IF(H3&gt;=1000,"Large",IF(H3&gt;=300,"Medium","Small"))</f>
@@ -660,7 +660,7 @@
         <v>2</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3332</v>
+        <v>3000</v>
       </c>
       <c r="I4">
         <f>IF(H4&gt;=1000,"Large",IF(H4&gt;=300,"Medium","Small"))</f>
@@ -709,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1454.4</v>
+        <v>1400</v>
       </c>
       <c r="I5">
         <f>IF(H5&gt;=1000,"Large",IF(H5&gt;=300,"Medium","Small"))</f>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>806</v>
+        <v>600</v>
       </c>
       <c r="I6">
         <f>IF(H6&gt;=1000,"Large",IF(H6&gt;=300,"Medium","Small"))</f>
@@ -807,7 +807,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1656</v>
+        <v>1600</v>
       </c>
       <c r="I7">
         <f>IF(H7&gt;=1000,"Large",IF(H7&gt;=300,"Medium","Small"))</f>
@@ -856,7 +856,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>326.25</v>
+        <v>300</v>
       </c>
       <c r="I8">
         <f>IF(H8&gt;=1000,"Large",IF(H8&gt;=300,"Medium","Small"))</f>
@@ -905,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
       <c r="I9">
         <f>IF(H9&gt;=1000,"Large",IF(H9&gt;=300,"Medium","Small"))</f>
@@ -954,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>587.2</v>
+        <v>600</v>
       </c>
       <c r="I10">
         <f>IF(H10&gt;=1000,"Large",IF(H10&gt;=300,"Medium","Small"))</f>
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>801.6</v>
+        <v>1200</v>
       </c>
       <c r="I11">
         <f>IF(H11&gt;=1000,"Large",IF(H11&gt;=300,"Medium","Small"))</f>
@@ -1052,7 +1052,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1663</v>
+        <v>1400</v>
       </c>
       <c r="I12">
         <f>IF(H12&gt;=1000,"Large",IF(H12&gt;=300,"Medium","Small"))</f>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>1037</v>
+        <v>600</v>
       </c>
       <c r="I13">
         <f>IF(H13&gt;=1000,"Large",IF(H13&gt;=300,"Medium","Small"))</f>
@@ -1132,7 +1132,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>724</v>
+        <v>800</v>
       </c>
       <c r="I14">
         <f>IF(H14&gt;=1000,"Large",IF(H14&gt;=300,"Medium","Small"))</f>
@@ -1172,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <f>IF(H15&gt;=1000,"Large",IF(H15&gt;=300,"Medium","Small"))</f>
@@ -1212,7 +1212,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>653.8</v>
+        <v>800</v>
       </c>
       <c r="I16">
         <f>IF(H16&gt;=1000,"Large",IF(H16&gt;=300,"Medium","Small"))</f>
@@ -1252,7 +1252,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
       <c r="I17">
         <f>IF(H17&gt;=1000,"Large",IF(H17&gt;=300,"Medium","Small"))</f>
@@ -1292,7 +1292,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>56.1</v>
+        <v>120</v>
       </c>
       <c r="I18">
         <f>IF(H18&gt;=1000,"Large",IF(H18&gt;=300,"Medium","Small"))</f>
@@ -1332,7 +1332,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>1148</v>
+        <v>1400</v>
       </c>
       <c r="I19">
         <f>IF(H19&gt;=1000,"Large",IF(H19&gt;=300,"Medium","Small"))</f>
@@ -1372,7 +1372,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>905.25</v>
+        <v>1400</v>
       </c>
       <c r="I20">
         <f>IF(H20&gt;=1000,"Large",IF(H20&gt;=300,"Medium","Small"))</f>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>918</v>
+        <v>600</v>
       </c>
       <c r="I21">
         <f>IF(H21&gt;=1000,"Large",IF(H21&gt;=300,"Medium","Small"))</f>
@@ -1452,7 +1452,7 @@
         <v>3</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>1806.9</v>
+        <v>1500</v>
       </c>
       <c r="I22">
         <f>IF(H22&gt;=1000,"Large",IF(H22&gt;=300,"Medium","Small"))</f>
@@ -1492,7 +1492,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>672.8</v>
+        <v>700</v>
       </c>
       <c r="I23">
         <f>IF(H23&gt;=1000,"Large",IF(H23&gt;=300,"Medium","Small"))</f>
@@ -1532,7 +1532,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>619.4</v>
+        <v>300</v>
       </c>
       <c r="I24">
         <f>IF(H24&gt;=1000,"Large",IF(H24&gt;=300,"Medium","Small"))</f>
@@ -1572,7 +1572,7 @@
         <v>2</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="I25">
         <f>IF(H25&gt;=1000,"Large",IF(H25&gt;=300,"Medium","Small"))</f>
@@ -1612,7 +1612,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>882</v>
+        <v>1400</v>
       </c>
       <c r="I26">
         <f>IF(H26&gt;=1000,"Large",IF(H26&gt;=300,"Medium","Small"))</f>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>190.8</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <f>IF(H27&gt;=1000,"Large",IF(H27&gt;=300,"Medium","Small"))</f>
@@ -1692,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>1696</v>
+        <v>1000</v>
       </c>
       <c r="I28">
         <f>IF(H28&gt;=1000,"Large",IF(H28&gt;=300,"Medium","Small"))</f>
@@ -1732,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>102.2</v>
+        <v>50</v>
       </c>
       <c r="I29">
         <f>IF(H29&gt;=1000,"Large",IF(H29&gt;=300,"Medium","Small"))</f>
@@ -1772,7 +1772,7 @@
         <v>2</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>258.4</v>
+        <v>240</v>
       </c>
       <c r="I30">
         <f>IF(H30&gt;=1000,"Large",IF(H30&gt;=300,"Medium","Small"))</f>
@@ -1812,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>263</v>
+        <v>200</v>
       </c>
       <c r="I31">
         <f>IF(H31&gt;=1000,"Large",IF(H31&gt;=300,"Medium","Small"))</f>

--- a/datasets/day1_excel_foundations/05_functions_and_data_tips/d1_m5_functions_answers.xlsx
+++ b/datasets/day1_excel_foundations/05_functions_and_data_tips/d1_m5_functions_answers.xlsx
@@ -461,13 +461,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
     <col width="19.5" customWidth="1" min="3" max="3"/>
-    <col width="10.5" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="L2" s="7">
-        <f>SUM(H2:H31)</f>
+        <f>SUM(H2:H21)</f>
         <v/>
       </c>
     </row>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="L3" s="7">
-        <f>AVERAGE(H2:H31)</f>
+        <f>AVERAGE(H2:H21)</f>
         <v/>
       </c>
     </row>
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="I4">
         <f>IF(H4&gt;=1000,"Large",IF(H4&gt;=300,"Medium","Small"))</f>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="L4" s="7">
-        <f>MAX(H2:H31)</f>
+        <f>MAX(H2:H21)</f>
         <v/>
       </c>
     </row>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1400</v>
+        <v>2800</v>
       </c>
       <c r="I5">
         <f>IF(H5&gt;=1000,"Large",IF(H5&gt;=300,"Medium","Small"))</f>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="L5" s="7">
-        <f>MIN(H2:H31)</f>
+        <f>MIN(H2:H21)</f>
         <v/>
       </c>
     </row>
@@ -746,19 +746,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I6">
         <f>IF(H6&gt;=1000,"Large",IF(H6&gt;=300,"Medium","Small"))</f>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="L6" s="8">
-        <f>COUNT(H2:H31)</f>
+        <f>COUNT(H2:H21)</f>
         <v/>
       </c>
     </row>
@@ -781,33 +781,33 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>45938</v>
+        <v>45694</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="I7">
         <f>IF(H7&gt;=1000,"Large",IF(H7&gt;=300,"Medium","Small"))</f>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="L7" s="8">
-        <f>SUM(G2:G31)</f>
+        <f>SUM(G2:G21)</f>
         <v/>
       </c>
     </row>
@@ -830,33 +830,33 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>45458</v>
+        <v>45922</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="I8">
         <f>IF(H8&gt;=1000,"Large",IF(H8&gt;=300,"Medium","Small"))</f>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="L8" s="8">
-        <f>COUNTIF(F2:F31,"Laptop")</f>
+        <f>COUNTIF(F2:F21,"Laptop")</f>
         <v/>
       </c>
     </row>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="L9" s="7">
-        <f>SUMIF(F2:F31,"Laptop",H2:H31)</f>
+        <f>SUMIF(F2:F21,"Laptop",H2:H21)</f>
         <v/>
       </c>
     </row>
@@ -928,11 +928,11 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>45856</v>
+        <v>46084</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -942,19 +942,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>USB-C Hub 7in1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="I10">
         <f>IF(H10&gt;=1000,"Large",IF(H10&gt;=300,"Medium","Small"))</f>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L10" s="8">
-        <f>COUNTIF(I2:I31,"Large")</f>
+        <f>COUNTIF(I2:I21,"Large")</f>
         <v/>
       </c>
     </row>
@@ -977,11 +977,11 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>45383</v>
+        <v>45796</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HP Spectre x360</t>
+          <t>Surface Go 4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="I11">
         <f>IF(H11&gt;=1000,"Large",IF(H11&gt;=300,"Medium","Small"))</f>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="L11" s="7">
-        <f>SUMIF(D2:D31,"Zimbabwe",H2:H31)</f>
+        <f>SUMIF(D2:D21,"Zimbabwe",H2:H21)</f>
         <v/>
       </c>
     </row>
@@ -1026,33 +1026,33 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46317</v>
+        <v>46200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Pixel 9 Pro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="I12">
         <f>IF(H12&gt;=1000,"Large",IF(H12&gt;=300,"Medium","Small"))</f>
@@ -1066,33 +1066,33 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>45857</v>
+        <v>45944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <f>IF(H13&gt;=1000,"Large",IF(H13&gt;=300,"Medium","Small"))</f>
@@ -1106,11 +1106,11 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>45994</v>
+        <v>46365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1120,19 +1120,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>HP Spectre x360</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
       <c r="I14">
         <f>IF(H14&gt;=1000,"Large",IF(H14&gt;=300,"Medium","Small"))</f>
@@ -1146,33 +1146,33 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>45453</v>
+        <v>45682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy Tab S10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="I15">
         <f>IF(H15&gt;=1000,"Large",IF(H15&gt;=300,"Medium","Small"))</f>
@@ -1186,33 +1186,33 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46287</v>
+        <v>46210</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Wireless Mouse Pro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="I16">
         <f>IF(H16&gt;=1000,"Large",IF(H16&gt;=300,"Medium","Small"))</f>
@@ -1226,33 +1226,33 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46107</v>
+        <v>45734</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>OnePlus 13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="I17">
         <f>IF(H17&gt;=1000,"Large",IF(H17&gt;=300,"Medium","Small"))</f>
@@ -1266,33 +1266,33 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46011</v>
+        <v>46347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tatenda Mpofu</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>Google Nest Hub 3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Accessory</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I18">
         <f>IF(H18&gt;=1000,"Large",IF(H18&gt;=300,"Medium","Small"))</f>
@@ -1306,11 +1306,11 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>45508</v>
+        <v>45902</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1320,19 +1320,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Laptop Sleeve 15in</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>1400</v>
+        <v>150</v>
       </c>
       <c r="I19">
         <f>IF(H19&gt;=1000,"Large",IF(H19&gt;=300,"Medium","Small"))</f>
@@ -1346,11 +1346,11 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>45671</v>
+        <v>46065</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1360,16 +1360,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>1400</v>
@@ -1386,11 +1386,11 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>45306</v>
+        <v>45824</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rutendo Chikafu</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1400,422 +1400,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="I21">
         <f>IF(H21&gt;=1000,"Large",IF(H21&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>O0021</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>45939</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Galaxy Tab S10</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I22">
-        <f>IF(H22&gt;=1000,"Large",IF(H22&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>O0022</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>45884</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>iPad Air 6</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="I23">
-        <f>IF(H23&gt;=1000,"Large",IF(H23&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>O0023</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>45522</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="I24">
-        <f>IF(H24&gt;=1000,"Large",IF(H24&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>O0024</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="I25">
-        <f>IF(H25&gt;=1000,"Large",IF(H25&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>O0025</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>46363</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ThinkPad X1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>1400</v>
-      </c>
-      <c r="I26">
-        <f>IF(H26&gt;=1000,"Large",IF(H26&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>O0026</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>46017</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Echo Dot 6</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="I27">
-        <f>IF(H27&gt;=1000,"Large",IF(H27&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>O0027</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>46252</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>MacBook Air M4</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I28">
-        <f>IF(H28&gt;=1000,"Large",IF(H28&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>O0028</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>46162</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Chipo Marufu</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Laptop Sleeve 15in</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="I29">
-        <f>IF(H29&gt;=1000,"Large",IF(H29&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>O0029</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>45498</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Bluetooth Headphones</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>240</v>
-      </c>
-      <c r="I30">
-        <f>IF(H30&gt;=1000,"Large",IF(H30&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>O0030</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>46183</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="I31">
-        <f>IF(H31&gt;=1000,"Large",IF(H31&gt;=300,"Medium","Small"))</f>
         <v/>
       </c>
     </row>
